--- a/ITARK_Spalte.xlsx
+++ b/ITARK_Spalte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\GS\GESV\20_GVS\Team\A-Team\30_Projects\30_ITAR-K\04_Column_tree\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Config\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E7E568-B8A6-45FD-BD74-A765F71DB9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{499E64D0-D6D4-4F08-BFC4-44A3F0BED07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{79E09D70-4644-4617-8D43-757B8DF2D3D7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{79E09D70-4644-4617-8D43-757B8DF2D3D7}"/>
   </bookViews>
   <sheets>
     <sheet name="ITARK_SPALTE" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3554,7 +3554,7 @@
         <v/>
       </c>
       <c r="Q3" s="39" t="str">
-        <f t="shared" ref="Q3:Q33" si="5">"IF "&amp;M3&amp;N3&amp;O3&amp;P3&amp;" THEN col = '"&amp;A3&amp;"';"</f>
+        <f t="shared" ref="Q3:Q34" si="5">"IF "&amp;M3&amp;N3&amp;O3&amp;P3&amp;" THEN col = '"&amp;A3&amp;"';"</f>
         <v>IF UV_TARIF = 1 AND UV_LIEGEKLASSE = 1 AND UV_GRUNDVERSICHERUNG = 1 THEN col = '1';</v>
       </c>
     </row>
@@ -5337,9 +5337,13 @@
         <f t="shared" ref="O34:O35" si="13">IF(I34 = "","",IF(ISERR(FIND(",",I34))," AND " &amp; I$1&amp;" = "&amp; I34, " AND " &amp; I$1&amp;" IN ("&amp; I34&amp;")"))</f>
         <v xml:space="preserve"> AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8)</v>
       </c>
+      <c r="P34" s="36" t="str">
+        <f t="shared" ref="P34:P35" si="14">IF(J34 = "","",IF(ISERR(FIND(",",J34))," AND " &amp; J$1&amp;" = '"&amp; J34&amp;"'", " AND " &amp; J$1&amp;" IN ("&amp; J34&amp;")"))</f>
+        <v xml:space="preserve"> AND UV_KTR_BESCHR = 'FOR'</v>
+      </c>
       <c r="Q34" s="37" t="str">
-        <f t="shared" ref="Q34:Q35" si="14">"IF "&amp;M34&amp;N34&amp;O34&amp;P34&amp;" THEN col = '"&amp;A34&amp;"';"</f>
-        <v>IF UV_TARIF IN (1,2,3,4,5,6,7) AND UV_LIEGEKLASSE = 1 AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8) THEN col = '30';</v>
+        <f t="shared" ref="Q34:Q35" si="15">"IF "&amp;M34&amp;N34&amp;O34&amp;P34&amp;" THEN col = '"&amp;A34&amp;"';"</f>
+        <v>IF UV_TARIF IN (1,2,3,4,5,6,7) AND UV_LIEGEKLASSE = 1 AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8) AND UV_KTR_BESCHR = 'FOR' THEN col = '30';</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="36" customFormat="1" x14ac:dyDescent="0.2">
@@ -5393,9 +5397,13 @@
         <f t="shared" si="13"/>
         <v xml:space="preserve"> AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8)</v>
       </c>
+      <c r="P35" s="36" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve"> AND UV_KTR_BESCHR = 'FOR'</v>
+      </c>
       <c r="Q35" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>IF UV_TARIF IN (1,2,3,4,5,6,7) AND UV_LIEGEKLASSE IN (2,3) AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8) THEN col = '31';</v>
+        <f t="shared" si="15"/>
+        <v>IF UV_TARIF IN (1,2,3,4,5,6,7) AND UV_LIEGEKLASSE IN (2,3) AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8) AND UV_KTR_BESCHR = 'FOR' THEN col = '31';</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
@@ -5427,31 +5435,31 @@
         <v>59</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" ref="K36" si="15">IF(E36 = "","",IF(ISERR(FIND(",",E36)),E$1&amp;" = "&amp; E36,E$1&amp;" IN ("&amp; E36&amp;")"))</f>
+        <f t="shared" ref="K36" si="16">IF(E36 = "","",IF(ISERR(FIND(",",E36)),E$1&amp;" = "&amp; E36,E$1&amp;" IN ("&amp; E36&amp;")"))</f>
         <v>UV_KTR_TYP = 1</v>
       </c>
       <c r="L36" t="str">
-        <f t="shared" ref="L36" si="16">IF(F36 = "","",IF(ISERR(FIND(",",F36))," AND " &amp; F$1&amp;" = '"&amp; F36&amp;"'", " AND " &amp; F$1&amp;" IN ("&amp; F36&amp;")"))</f>
+        <f t="shared" ref="L36" si="17">IF(F36 = "","",IF(ISERR(FIND(",",F36))," AND " &amp; F$1&amp;" = '"&amp; F36&amp;"'", " AND " &amp; F$1&amp;" IN ("&amp; F36&amp;")"))</f>
         <v xml:space="preserve"> AND UV_ABC_FALL = 'A'</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" ref="M36" si="17">IF(G36 = "","",IF(ISERR(FIND(",",G36)),G$1&amp;" = "&amp; G36, G$1&amp;" IN ("&amp; G36&amp;")"))</f>
+        <f t="shared" ref="M36" si="18">IF(G36 = "","",IF(ISERR(FIND(",",G36)),G$1&amp;" = "&amp; G36, G$1&amp;" IN ("&amp; G36&amp;")"))</f>
         <v>UV_TARIF = 7</v>
       </c>
       <c r="N36" t="str">
-        <f t="shared" ref="N36:O36" si="18">IF(H36 = "","",IF(ISERR(FIND(",",H36))," AND " &amp; H$1&amp;" = "&amp; H36, " AND " &amp; H$1&amp;" IN ("&amp; H36&amp;")"))</f>
+        <f t="shared" ref="N36:O36" si="19">IF(H36 = "","",IF(ISERR(FIND(",",H36))," AND " &amp; H$1&amp;" = "&amp; H36, " AND " &amp; H$1&amp;" IN ("&amp; H36&amp;")"))</f>
         <v xml:space="preserve"> AND UV_LIEGEKLASSE IN (1,2,3)</v>
       </c>
       <c r="O36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve"> AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8)</v>
       </c>
       <c r="P36" t="str">
-        <f t="shared" ref="P36" si="19">IF(J36="",""," AND " &amp; J36&amp;"(" &amp; J$1 &amp; ")")</f>
+        <f t="shared" ref="P36" si="20">IF(J36="",""," AND " &amp; J36&amp;"(" &amp; J$1 &amp; ")")</f>
         <v/>
       </c>
       <c r="Q36" s="39" t="str">
-        <f t="shared" ref="Q36" si="20">"IF "&amp;M36&amp;N36&amp;O36&amp;P36&amp;" THEN col = '"&amp;A36&amp;"';"</f>
+        <f t="shared" ref="Q36" si="21">"IF "&amp;M36&amp;N36&amp;O36&amp;P36&amp;" THEN col = '"&amp;A36&amp;"';"</f>
         <v>IF UV_TARIF = 7 AND UV_LIEGEKLASSE IN (1,2,3) AND UV_GRUNDVERSICHERUNG IN (1,2,3,4,5,8) THEN col = '32';</v>
       </c>
     </row>
@@ -5498,7 +5506,7 @@
       <c r="I38" s="43"/>
       <c r="J38" s="43"/>
       <c r="K38" s="42" t="str">
-        <f t="shared" ref="K38:K96" si="21">IF(E38 = "","",IF(ISERR(FIND(",",E38)),E$1&amp;" = "&amp; E38,E$1&amp;" IN ("&amp; E38&amp;")"))</f>
+        <f t="shared" ref="K38:K96" si="22">IF(E38 = "","",IF(ISERR(FIND(",",E38)),E$1&amp;" = "&amp; E38,E$1&amp;" IN ("&amp; E38&amp;")"))</f>
         <v>UV_KTR_TYP = 101</v>
       </c>
       <c r="L38" s="42"/>
@@ -5507,7 +5515,7 @@
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="39" t="str">
-        <f t="shared" ref="Q38:Q55" si="22">"IF "&amp;K38&amp;L38&amp;M38&amp;N38&amp;O38&amp;P38&amp;" THEN col = '"&amp;A38&amp;"';"</f>
+        <f t="shared" ref="Q38:Q55" si="23">"IF "&amp;K38&amp;L38&amp;M38&amp;N38&amp;O38&amp;P38&amp;" THEN col = '"&amp;A38&amp;"';"</f>
         <v>IF UV_KTR_TYP = 101 THEN col = '32';</v>
       </c>
     </row>
@@ -5529,7 +5537,7 @@
       <c r="I39" s="46"/>
       <c r="J39" s="46"/>
       <c r="K39" s="45" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = abandon</v>
       </c>
       <c r="L39" s="45"/>
@@ -5538,7 +5546,7 @@
       <c r="O39" s="45"/>
       <c r="P39" s="45"/>
       <c r="Q39" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = abandon THEN col = '';</v>
       </c>
     </row>
@@ -5559,11 +5567,11 @@
         <v>102</v>
       </c>
       <c r="K40" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 102</v>
       </c>
       <c r="Q40" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 102 THEN col = '34';</v>
       </c>
     </row>
@@ -5584,11 +5592,11 @@
         <v>201</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 201</v>
       </c>
       <c r="Q41" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 201 THEN col = '35';</v>
       </c>
     </row>
@@ -5609,11 +5617,11 @@
         <v>202</v>
       </c>
       <c r="K42" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 202</v>
       </c>
       <c r="Q42" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 202 THEN col = '36';</v>
       </c>
     </row>
@@ -5634,11 +5642,11 @@
         <v>203</v>
       </c>
       <c r="K43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 203</v>
       </c>
       <c r="Q43" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 203 THEN col = '37';</v>
       </c>
     </row>
@@ -5659,11 +5667,11 @@
         <v>204</v>
       </c>
       <c r="K44" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 204</v>
       </c>
       <c r="Q44" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 204 THEN col = '38';</v>
       </c>
     </row>
@@ -5684,11 +5692,11 @@
         <v>205</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 205</v>
       </c>
       <c r="Q45" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 205 THEN col = '39';</v>
       </c>
     </row>
@@ -5709,11 +5717,11 @@
         <v>206</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 206</v>
       </c>
       <c r="Q46" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 206 THEN col = '40';</v>
       </c>
     </row>
@@ -5734,11 +5742,11 @@
         <v>207</v>
       </c>
       <c r="K47" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 207</v>
       </c>
       <c r="Q47" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 207 THEN col = '41';</v>
       </c>
     </row>
@@ -5759,11 +5767,11 @@
         <v>291</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 291</v>
       </c>
       <c r="Q48" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 291 THEN col = '42';</v>
       </c>
     </row>
@@ -5784,11 +5792,11 @@
         <v>292</v>
       </c>
       <c r="K49" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 292</v>
       </c>
       <c r="Q49" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 292 THEN col = '43';</v>
       </c>
     </row>
@@ -5809,11 +5817,11 @@
         <v>293</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 293</v>
       </c>
       <c r="Q50" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 293 THEN col = '44';</v>
       </c>
     </row>
@@ -5834,11 +5842,11 @@
         <v>294</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 294</v>
       </c>
       <c r="Q51" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 294 THEN col = '45';</v>
       </c>
     </row>
@@ -5859,11 +5867,11 @@
         <v>251</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 251</v>
       </c>
       <c r="Q52" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 251 THEN col = '46';</v>
       </c>
     </row>
@@ -5884,11 +5892,11 @@
         <v>252</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 252</v>
       </c>
       <c r="Q53" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 252 THEN col = '47';</v>
       </c>
     </row>
@@ -5909,11 +5917,11 @@
         <v>253</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 253</v>
       </c>
       <c r="Q54" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP = 253 THEN col = '48';</v>
       </c>
     </row>
@@ -5934,11 +5942,11 @@
         <v>33</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (601,602,603)</v>
       </c>
       <c r="Q55" s="39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>IF UV_KTR_TYP IN (601,602,603) THEN col = '49';</v>
       </c>
     </row>
@@ -5959,7 +5967,7 @@
         <v>34</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (5**,7**)</v>
       </c>
       <c r="Q56" s="39" t="s">
@@ -5983,11 +5991,11 @@
         <v>801</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 801</v>
       </c>
       <c r="Q57" s="39" t="str">
-        <f t="shared" ref="Q57:Q63" si="23">"IF "&amp;K57&amp;L57&amp;M57&amp;N57&amp;O57&amp;P57&amp;" THEN col = '"&amp;A57&amp;"';"</f>
+        <f t="shared" ref="Q57:Q63" si="24">"IF "&amp;K57&amp;L57&amp;M57&amp;N57&amp;O57&amp;P57&amp;" THEN col = '"&amp;A57&amp;"';"</f>
         <v>IF UV_KTR_TYP = 801 THEN col = '51';</v>
       </c>
     </row>
@@ -6013,11 +6021,11 @@
       <c r="I58" s="32"/>
       <c r="J58" s="32"/>
       <c r="K58" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 301</v>
       </c>
       <c r="Q58" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 301 THEN col = '52';</v>
       </c>
     </row>
@@ -6043,11 +6051,11 @@
       <c r="I59" s="32"/>
       <c r="J59" s="32"/>
       <c r="K59" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 302</v>
       </c>
       <c r="Q59" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 302 THEN col = '53';</v>
       </c>
     </row>
@@ -6073,11 +6081,11 @@
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 303</v>
       </c>
       <c r="Q60" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 303 THEN col = '54';</v>
       </c>
     </row>
@@ -6103,11 +6111,11 @@
       <c r="I61" s="33"/>
       <c r="J61" s="33"/>
       <c r="K61" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 330</v>
       </c>
       <c r="Q61" s="37" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 330 THEN col = '100';</v>
       </c>
     </row>
@@ -6133,11 +6141,11 @@
       <c r="I62" s="33"/>
       <c r="J62" s="33"/>
       <c r="K62" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 331</v>
       </c>
       <c r="Q62" s="37" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 331 THEN col = '101';</v>
       </c>
     </row>
@@ -6163,11 +6171,11 @@
       <c r="I63" s="33"/>
       <c r="J63" s="33"/>
       <c r="K63" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 332</v>
       </c>
       <c r="Q63" s="37" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>IF UV_KTR_TYP = 332 THEN col = '102';</v>
       </c>
     </row>
@@ -6193,11 +6201,11 @@
       <c r="I64" s="33"/>
       <c r="J64" s="33"/>
       <c r="K64" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 333</v>
       </c>
       <c r="Q64" s="37" t="str">
-        <f t="shared" ref="Q64:Q96" si="24">"IF "&amp;K64&amp;L64&amp;M64&amp;N64&amp;O64&amp;P64&amp;" THEN col = '"&amp;A64&amp;"';"</f>
+        <f t="shared" ref="Q64:Q96" si="25">"IF "&amp;K64&amp;L64&amp;M64&amp;N64&amp;O64&amp;P64&amp;" THEN col = '"&amp;A64&amp;"';"</f>
         <v>IF UV_KTR_TYP = 333 THEN col = '103';</v>
       </c>
     </row>
@@ -6223,11 +6231,11 @@
       <c r="I65" s="33"/>
       <c r="J65" s="33"/>
       <c r="K65" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 334</v>
       </c>
       <c r="Q65" s="37" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 334 THEN col = '104';</v>
       </c>
     </row>
@@ -6253,11 +6261,11 @@
       <c r="I66" s="33"/>
       <c r="J66" s="33"/>
       <c r="K66" s="36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 335</v>
       </c>
       <c r="Q66" s="37" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 335 THEN col = '105';</v>
       </c>
     </row>
@@ -6278,11 +6286,11 @@
         <v>304</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 304</v>
       </c>
       <c r="Q67" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 304 THEN col = '55';</v>
       </c>
     </row>
@@ -6303,11 +6311,11 @@
         <v>305</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 305</v>
       </c>
       <c r="Q68" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 305 THEN col = '56';</v>
       </c>
     </row>
@@ -6328,11 +6336,11 @@
         <v>306</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 306</v>
       </c>
       <c r="Q69" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 306 THEN col = '57';</v>
       </c>
     </row>
@@ -6353,11 +6361,11 @@
         <v>307</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 307</v>
       </c>
       <c r="Q70" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 307 THEN col = '58';</v>
       </c>
     </row>
@@ -6378,11 +6386,11 @@
         <v>308</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 308</v>
       </c>
       <c r="Q71" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 308 THEN col = '59';</v>
       </c>
     </row>
@@ -6403,11 +6411,11 @@
         <v>309</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 309</v>
       </c>
       <c r="Q72" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 309 THEN col = '60';</v>
       </c>
     </row>
@@ -6428,11 +6436,11 @@
         <v>310</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 310</v>
       </c>
       <c r="Q73" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 310 THEN col = '61';</v>
       </c>
     </row>
@@ -6453,11 +6461,11 @@
         <v>311</v>
       </c>
       <c r="K74" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 311</v>
       </c>
       <c r="Q74" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 311 THEN col = '62';</v>
       </c>
     </row>
@@ -6478,11 +6486,11 @@
         <v>312</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 312</v>
       </c>
       <c r="Q75" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 312 THEN col = '63';</v>
       </c>
     </row>
@@ -6503,11 +6511,11 @@
         <v>313</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 313</v>
       </c>
       <c r="Q76" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 313 THEN col = '64';</v>
       </c>
     </row>
@@ -6528,11 +6536,11 @@
         <v>314</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 314</v>
       </c>
       <c r="Q77" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 314 THEN col = '65';</v>
       </c>
     </row>
@@ -6553,11 +6561,11 @@
         <v>315</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 315</v>
       </c>
       <c r="Q78" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 315 THEN col = '66';</v>
       </c>
     </row>
@@ -6578,11 +6586,11 @@
         <v>316</v>
       </c>
       <c r="K79" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 316</v>
       </c>
       <c r="Q79" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 316 THEN col = '67';</v>
       </c>
     </row>
@@ -6603,11 +6611,11 @@
         <v>317</v>
       </c>
       <c r="K80" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 317</v>
       </c>
       <c r="Q80" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 317 THEN col = '68';</v>
       </c>
     </row>
@@ -6628,11 +6636,11 @@
         <v>318</v>
       </c>
       <c r="K81" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 318</v>
       </c>
       <c r="Q81" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 318 THEN col = '69';</v>
       </c>
     </row>
@@ -6653,11 +6661,11 @@
         <v>319</v>
       </c>
       <c r="K82" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 319</v>
       </c>
       <c r="Q82" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 319 THEN col = '70';</v>
       </c>
     </row>
@@ -6678,11 +6686,11 @@
         <v>320</v>
       </c>
       <c r="K83" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 320</v>
       </c>
       <c r="Q83" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 320 THEN col = '71';</v>
       </c>
     </row>
@@ -6703,11 +6711,11 @@
         <v>321</v>
       </c>
       <c r="K84" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 321</v>
       </c>
       <c r="Q84" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 321 THEN col = '72';</v>
       </c>
     </row>
@@ -6728,11 +6736,11 @@
         <v>322</v>
       </c>
       <c r="K85" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 322</v>
       </c>
       <c r="Q85" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 322 THEN col = '73';</v>
       </c>
     </row>
@@ -6753,11 +6761,11 @@
         <v>323</v>
       </c>
       <c r="K86" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 323</v>
       </c>
       <c r="Q86" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 323 THEN col = '74';</v>
       </c>
     </row>
@@ -6778,11 +6786,11 @@
         <v>324</v>
       </c>
       <c r="K87" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 324</v>
       </c>
       <c r="Q87" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 324 THEN col = '75';</v>
       </c>
     </row>
@@ -6803,11 +6811,11 @@
         <v>325</v>
       </c>
       <c r="K88" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 325</v>
       </c>
       <c r="Q88" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 325 THEN col = '76';</v>
       </c>
     </row>
@@ -6828,11 +6836,11 @@
         <v>326</v>
       </c>
       <c r="K89" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 326</v>
       </c>
       <c r="Q89" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 326 THEN col = '77';</v>
       </c>
     </row>
@@ -6853,11 +6861,11 @@
         <v>199</v>
       </c>
       <c r="K90" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (371,372,373)</v>
       </c>
       <c r="Q90" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP IN (371,372,373) THEN col = '78';</v>
       </c>
     </row>
@@ -6878,11 +6886,11 @@
         <v>200</v>
       </c>
       <c r="K91" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (374,375,376)</v>
       </c>
       <c r="Q91" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP IN (374,375,376) THEN col = '79';</v>
       </c>
     </row>
@@ -6903,11 +6911,11 @@
         <v>201</v>
       </c>
       <c r="K92" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (377,378,379)</v>
       </c>
       <c r="Q92" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP IN (377,378,379) THEN col = '80';</v>
       </c>
     </row>
@@ -6929,11 +6937,11 @@
       </c>
       <c r="F93"/>
       <c r="K93" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP IN (380,381,382,402,301,302,303)</v>
       </c>
       <c r="Q93" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP IN (380,381,382,402,301,302,303) THEN col = '81';</v>
       </c>
     </row>
@@ -6954,11 +6962,11 @@
         <v>383</v>
       </c>
       <c r="K94" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 383</v>
       </c>
       <c r="Q94" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 383 THEN col = '82';</v>
       </c>
     </row>
@@ -6979,11 +6987,11 @@
         <v>401</v>
       </c>
       <c r="K95" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 401</v>
       </c>
       <c r="Q95" s="39" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 401 THEN col = '83';</v>
       </c>
     </row>
@@ -7009,7 +7017,7 @@
       <c r="I96" s="49"/>
       <c r="J96" s="49"/>
       <c r="K96" s="48" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>UV_KTR_TYP = 403</v>
       </c>
       <c r="L96" s="48"/>
@@ -7018,7 +7026,7 @@
       <c r="O96" s="48"/>
       <c r="P96" s="48"/>
       <c r="Q96" s="50" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>IF UV_KTR_TYP = 403 THEN col = '84';</v>
       </c>
     </row>
@@ -7029,6 +7037,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A06AEA027BD58C449ED682CA790C1DA1" ma:contentTypeVersion="2" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="039b129cb7113286d5d2e514601927ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ea3fe04-ef4e-4152-93e9-94f34b722c58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b99f6e70900da4e46a666e3a012647e6" ns2:_="">
     <xsd:import namespace="4ea3fe04-ef4e-4152-93e9-94f34b722c58"/>
@@ -7176,22 +7199,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{509CC551-1A86-45E2-82C3-1F73E28226EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4ea3fe04-ef4e-4152-93e9-94f34b722c58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0769FD26-CF86-4A1B-AB28-BDFC1EBE0087}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF44961C-4A32-4E96-A9D7-86A6AAB7D67A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7207,28 +7239,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0769FD26-CF86-4A1B-AB28-BDFC1EBE0087}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{509CC551-1A86-45E2-82C3-1F73E28226EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4ea3fe04-ef4e-4152-93e9-94f34b722c58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>